--- a/backend/data/financials_by_company/0361.HK.xlsx
+++ b/backend/data/financials_by_company/0361.HK.xlsx
@@ -3975,7 +3975,7 @@
         <v>-24579000</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
         <v>0.58</v>
@@ -4185,7 +4185,7 @@
         <v>0</v>
       </c>
       <c r="DU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV2" t="n">
         <v>-0.008500002</v>
